--- a/output/pdf_financials_xlsx/IRI.xlsx
+++ b/output/pdf_financials_xlsx/IRI.xlsx
@@ -6000,43 +6000,43 @@
         <v>0.463495</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.615324</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.658645</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.713867</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.713867</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.713867</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.713867</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.827603</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.827603</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.827603</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.827603</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.827603</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.827603</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.827603</v>
       </c>
     </row>
     <row r="93">
@@ -9815,7 +9815,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -12505,7 +12509,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/IRI.xlsx
+++ b/output/pdf_financials_xlsx/IRI.xlsx
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.1e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>6.8e-05</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000109</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1092,28 +1092,28 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000935</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.008579</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.003552</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000168</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000104</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000263</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000307</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.000212</v>
       </c>
     </row>
     <row r="13">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.099201</v>
+        <v>-0.09921199999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.200572</v>
+        <v>-0.20064</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>-0.264129</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.339958</v>
+        <v>-2.340067</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.442637</v>
@@ -2100,28 +2100,28 @@
         <v>-0.112191</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.623763</v>
+        <v>0.622828</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.207294</v>
+        <v>-0.215873</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.077692</v>
+        <v>-0.081244</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.098283</v>
+        <v>-0.098451</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.054249</v>
+        <v>-0.054353</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.134695</v>
+        <v>-0.134958</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.587264</v>
+        <v>-2.587571</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.166569</v>
+        <v>-0.166781</v>
       </c>
     </row>
     <row r="28">
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.099201</v>
+        <v>-0.09921199999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.200572</v>
+        <v>-0.20064</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>-0.264129</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.339958</v>
+        <v>-2.340067</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.442637</v>
@@ -2224,28 +2224,28 @@
         <v>-0.112191</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.623763</v>
+        <v>0.622828</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.207294</v>
+        <v>-0.215873</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.077692</v>
+        <v>-0.081244</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.098283</v>
+        <v>-0.098451</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.054249</v>
+        <v>-0.054353</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.134695</v>
+        <v>-0.134958</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.587264</v>
+        <v>-2.587571</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.166569</v>
+        <v>-0.166781</v>
       </c>
     </row>
     <row r="30">
@@ -2526,37 +2526,37 @@
         <v>0.014468</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.009488999999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.003998</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.168308</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.222178</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.251423</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.127695</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.8180539999999999</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.739273</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.591606</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.361929</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.12023</v>
       </c>
     </row>
     <row r="35">
@@ -2642,37 +2642,37 @@
         <v>0.014468</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.009488999999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.003998</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.662435</v>
+        <v>0.830743</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.005325</v>
+        <v>0.227503</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.251423</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.127695</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.8180539999999999</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.739273</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.591606</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.361929</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.12023</v>
       </c>
     </row>
     <row r="37">
@@ -3338,37 +3338,37 @@
         <v>0.005234</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.009488999999999999</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.007865</v>
+        <v>0.003867</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.174282</v>
+        <v>0.005974</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.412283</v>
+        <v>1.190105</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.261461</v>
+        <v>0.010038</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.135887</v>
+        <v>0.008192</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.822875</v>
+        <v>0.004821</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.7446390000000001</v>
+        <v>0.005366</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.60226</v>
+        <v>0.010654</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.370257</v>
+        <v>0.008328</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.3167</v>
+        <v>0.19647</v>
       </c>
     </row>
     <row r="49">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -38495,7 +38495,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E304" s="5" t="n">

--- a/output/pdf_financials_xlsx/IRI.xlsx
+++ b/output/pdf_financials_xlsx/IRI.xlsx
@@ -7579,16 +7579,16 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.400001</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.293</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>2.680056</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>0.021429</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -34787,7 +34787,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -37401,7 +37405,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E292" s="5" t="n">
         <v>0.400001</v>
       </c>

--- a/output/pdf_financials_xlsx/IRI.xlsx
+++ b/output/pdf_financials_xlsx/IRI.xlsx
@@ -1331,7 +1331,7 @@
         <v>-2.339958</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-0.442637</v>
+        <v>-0.423234</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.479089</v>
@@ -1393,7 +1393,7 @@
         <v>-0.03007</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.019403</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -2091,7 +2091,7 @@
         <v>-2.340067</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.442637</v>
+        <v>-0.423234</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.479089</v>
@@ -2215,7 +2215,7 @@
         <v>-2.340067</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.442637</v>
+        <v>-0.423234</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.479089</v>
@@ -2369,7 +2369,7 @@
         <v>-1.285065800326331</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.584461550820587</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -6475,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009103999999999999</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -7299,13 +7299,13 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.220058</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>1.332302</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.005166</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -27019,7 +27019,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -27896,7 +27900,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -31100,7 +31108,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -34187,7 +34199,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -44702,7 +44718,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -45898,7 +45918,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
